--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -1010,54 +1010,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130228818</v>
+        <v>130229588</v>
       </c>
       <c r="B5" t="n">
-        <v>91939</v>
+        <v>97706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>224363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540122</v>
+        <v>540144</v>
       </c>
       <c r="R5" t="n">
-        <v>6703952</v>
+        <v>6703908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På yta cirka 6x7 meter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,41 +1118,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130229588</v>
+        <v>130228818</v>
       </c>
       <c r="B6" t="n">
-        <v>97706</v>
+        <v>91939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540144</v>
+        <v>540122</v>
       </c>
       <c r="R6" t="n">
-        <v>6703908</v>
+        <v>6703952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På yta cirka 6x7 meter.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130228529</v>
+        <v>130228096</v>
       </c>
       <c r="B7" t="n">
         <v>91641</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540105</v>
+        <v>540116</v>
       </c>
       <c r="R7" t="n">
-        <v>6703987</v>
+        <v>6704044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228096</v>
+        <v>130228529</v>
       </c>
       <c r="B8" t="n">
         <v>91641</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540116</v>
+        <v>540105</v>
       </c>
       <c r="R8" t="n">
-        <v>6704044</v>
+        <v>6703986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130228342</v>
+        <v>130229386</v>
       </c>
       <c r="B17" t="n">
-        <v>91641</v>
+        <v>91939</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,34 +2369,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540101</v>
+        <v>540214</v>
       </c>
       <c r="R17" t="n">
-        <v>6704020</v>
+        <v>6703919</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2438,7 +2447,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,7 +2479,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130229386</v>
+        <v>130228851</v>
       </c>
       <c r="B18" t="n">
         <v>91939</v>
@@ -2493,26 +2507,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540214</v>
+        <v>540110</v>
       </c>
       <c r="R18" t="n">
-        <v>6703919</v>
+        <v>6703934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2554,12 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,54 +2586,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130229568</v>
+        <v>130228342</v>
       </c>
       <c r="B19" t="n">
-        <v>97710</v>
+        <v>91641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540146</v>
+        <v>540101</v>
       </c>
       <c r="R19" t="n">
-        <v>6703912</v>
+        <v>6704020</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,12 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130229109</v>
+        <v>130229568</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>97710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,27 +2704,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2747,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540125</v>
+        <v>540146</v>
       </c>
       <c r="R20" t="n">
-        <v>6703913</v>
+        <v>6703912</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,7 +2772,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2792,7 +2782,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,45 +2814,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130228851</v>
+        <v>130229109</v>
       </c>
       <c r="B21" t="n">
-        <v>91939</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540110</v>
+        <v>540125</v>
       </c>
       <c r="R21" t="n">
-        <v>6703934</v>
+        <v>6703913</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,7 +2973,7 @@
         <v>540105</v>
       </c>
       <c r="R22" t="n">
-        <v>6703987</v>
+        <v>6703986</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3149,54 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229093</v>
+        <v>130229622</v>
       </c>
       <c r="B24" t="n">
-        <v>91939</v>
+        <v>97707</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540129</v>
+        <v>540146</v>
       </c>
       <c r="R24" t="n">
-        <v>6703915</v>
+        <v>6703918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3229,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,45 +3261,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229622</v>
+        <v>130229093</v>
       </c>
       <c r="B25" t="n">
-        <v>97707</v>
+        <v>91939</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540146</v>
+        <v>540129</v>
       </c>
       <c r="R25" t="n">
-        <v>6703918</v>
+        <v>6703915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3335,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,12 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130229287</v>
       </c>
       <c r="B3" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130227543</v>
       </c>
       <c r="B4" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,41 +1010,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130229588</v>
+        <v>130228818</v>
       </c>
       <c r="B5" t="n">
-        <v>97706</v>
+        <v>92026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540144</v>
+        <v>540122</v>
       </c>
       <c r="R5" t="n">
-        <v>6703908</v>
+        <v>6703952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På yta cirka 6x7 meter.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,54 +1126,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130228818</v>
+        <v>130229588</v>
       </c>
       <c r="B6" t="n">
-        <v>91939</v>
+        <v>97793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540122</v>
+        <v>540144</v>
       </c>
       <c r="R6" t="n">
-        <v>6703952</v>
+        <v>6703908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1202,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På yta cirka 6x7 meter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>130228096</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>130228529</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,59 +1448,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130232204</v>
+        <v>130228618</v>
       </c>
       <c r="B9" t="n">
-        <v>97710</v>
+        <v>92026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540145</v>
+        <v>540118</v>
       </c>
       <c r="R9" t="n">
-        <v>6703918</v>
+        <v>6703975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,56 +1567,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130228618</v>
+        <v>130232204</v>
       </c>
       <c r="B10" t="n">
-        <v>91939</v>
+        <v>97797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540118</v>
+        <v>540145</v>
       </c>
       <c r="R10" t="n">
-        <v>6703975</v>
+        <v>6703918</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>130227983</v>
       </c>
       <c r="B11" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130229042</v>
+        <v>130228156</v>
       </c>
       <c r="B12" t="n">
-        <v>91641</v>
+        <v>92026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540141</v>
+        <v>540107</v>
       </c>
       <c r="R12" t="n">
-        <v>6703928</v>
+        <v>6704044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228156</v>
+        <v>130228270</v>
       </c>
       <c r="B13" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1941,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1946,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540107</v>
+        <v>540094</v>
       </c>
       <c r="R13" t="n">
-        <v>6704044</v>
+        <v>6704020</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,7 +2000,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ovanligt stora fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228270</v>
+        <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>91939</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,43 +2043,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540094</v>
+        <v>540141</v>
       </c>
       <c r="R14" t="n">
-        <v>6704020</v>
+        <v>6703928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,12 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ovanligt stora fruktkroppar.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,7 +2142,7 @@
         <v>130229463</v>
       </c>
       <c r="B15" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>130227990</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>130229386</v>
       </c>
       <c r="B17" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130228851</v>
+        <v>130228342</v>
       </c>
       <c r="B18" t="n">
-        <v>91939</v>
+        <v>91728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540110</v>
+        <v>540101</v>
       </c>
       <c r="R18" t="n">
-        <v>6703934</v>
+        <v>6704020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,45 +2586,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130228342</v>
+        <v>130229568</v>
       </c>
       <c r="B19" t="n">
-        <v>91641</v>
+        <v>97797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540101</v>
+        <v>540146</v>
       </c>
       <c r="R19" t="n">
-        <v>6704020</v>
+        <v>6703912</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2675,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,10 +2707,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130229568</v>
+        <v>130229109</v>
       </c>
       <c r="B20" t="n">
-        <v>97710</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,31 +2718,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2737,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540146</v>
+        <v>540125</v>
       </c>
       <c r="R20" t="n">
-        <v>6703912</v>
+        <v>6703913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,7 +2782,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2782,12 +2792,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,50 +2819,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130229109</v>
+        <v>130228851</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>92026</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540125</v>
+        <v>540110</v>
       </c>
       <c r="R21" t="n">
-        <v>6703913</v>
+        <v>6703934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,7 +2929,7 @@
         <v>130228509</v>
       </c>
       <c r="B22" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>130228323</v>
       </c>
       <c r="B23" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>130229622</v>
       </c>
       <c r="B24" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3261,54 +3261,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229093</v>
+        <v>130227845</v>
       </c>
       <c r="B25" t="n">
-        <v>91939</v>
+        <v>91110</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540129</v>
+        <v>540093</v>
       </c>
       <c r="R25" t="n">
-        <v>6703915</v>
+        <v>6704106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3344,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3359,6 +3358,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3377,48 +3377,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130227845</v>
+        <v>130229093</v>
       </c>
       <c r="B26" t="n">
-        <v>91023</v>
+        <v>92026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5685</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540093</v>
+        <v>540129</v>
       </c>
       <c r="R26" t="n">
-        <v>6704106</v>
+        <v>6703915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3456,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,12 +3466,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,7 +3475,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229622</v>
+        <v>130227845</v>
       </c>
       <c r="B24" t="n">
-        <v>97794</v>
+        <v>91110</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,34 +3160,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540146</v>
+        <v>540093</v>
       </c>
       <c r="R24" t="n">
-        <v>6703918</v>
+        <v>6704106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,12 +3232,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,6 +3246,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3261,48 +3265,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227845</v>
+        <v>130229093</v>
       </c>
       <c r="B25" t="n">
-        <v>91110</v>
+        <v>92026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5685</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540093</v>
+        <v>540129</v>
       </c>
       <c r="R25" t="n">
-        <v>6704106</v>
+        <v>6703915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3334,7 +3344,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,12 +3354,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3358,7 +3363,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3377,54 +3381,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130229093</v>
+        <v>130229622</v>
       </c>
       <c r="B26" t="n">
-        <v>92026</v>
+        <v>97794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>221946</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540129</v>
+        <v>540146</v>
       </c>
       <c r="R26" t="n">
-        <v>6703915</v>
+        <v>6703918</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3466,7 +3461,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -1010,54 +1010,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130228818</v>
+        <v>130229588</v>
       </c>
       <c r="B5" t="n">
-        <v>92026</v>
+        <v>97793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>224363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540122</v>
+        <v>540144</v>
       </c>
       <c r="R5" t="n">
-        <v>6703952</v>
+        <v>6703908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På yta cirka 6x7 meter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,41 +1118,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130229588</v>
+        <v>130228818</v>
       </c>
       <c r="B6" t="n">
-        <v>97793</v>
+        <v>92026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540144</v>
+        <v>540122</v>
       </c>
       <c r="R6" t="n">
-        <v>6703908</v>
+        <v>6703952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På yta cirka 6x7 meter.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130228096</v>
+        <v>130228529</v>
       </c>
       <c r="B7" t="n">
         <v>91728</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540116</v>
+        <v>540105</v>
       </c>
       <c r="R7" t="n">
-        <v>6704044</v>
+        <v>6703987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228529</v>
+        <v>130228096</v>
       </c>
       <c r="B8" t="n">
         <v>91728</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540105</v>
+        <v>540116</v>
       </c>
       <c r="R8" t="n">
-        <v>6703986</v>
+        <v>6704044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228156</v>
+        <v>130229042</v>
       </c>
       <c r="B12" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,43 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540107</v>
+        <v>540141</v>
       </c>
       <c r="R12" t="n">
-        <v>6704044</v>
+        <v>6703928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130229042</v>
+        <v>130228156</v>
       </c>
       <c r="B14" t="n">
-        <v>91728</v>
+        <v>92026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,34 +2034,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540141</v>
+        <v>540107</v>
       </c>
       <c r="R14" t="n">
-        <v>6703928</v>
+        <v>6704044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2358,54 +2358,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130229386</v>
+        <v>130229568</v>
       </c>
       <c r="B17" t="n">
-        <v>92026</v>
+        <v>97797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540214</v>
+        <v>540146</v>
       </c>
       <c r="R17" t="n">
-        <v>6703919</v>
+        <v>6703912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130228342</v>
+        <v>130229386</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>92026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,34 +2490,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540101</v>
+        <v>540214</v>
       </c>
       <c r="R18" t="n">
-        <v>6704020</v>
+        <v>6703919</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2568,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,54 +2600,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130229568</v>
+        <v>130228342</v>
       </c>
       <c r="B19" t="n">
-        <v>97797</v>
+        <v>91728</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540146</v>
+        <v>540101</v>
       </c>
       <c r="R19" t="n">
-        <v>6703912</v>
+        <v>6704020</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,7 +2670,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,12 +2680,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2926,7 +2926,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B22" t="n">
         <v>92026</v>
@@ -2954,26 +2954,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R22" t="n">
-        <v>6703986</v>
+        <v>6704022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +2996,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3006,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,7 +3033,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B23" t="n">
         <v>92026</v>
@@ -3070,17 +3061,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R23" t="n">
-        <v>6704022</v>
+        <v>6703987</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,54 +3265,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229093</v>
+        <v>130229622</v>
       </c>
       <c r="B25" t="n">
-        <v>92026</v>
+        <v>97794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540129</v>
+        <v>540146</v>
       </c>
       <c r="R25" t="n">
-        <v>6703915</v>
+        <v>6703918</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3345,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,45 +3377,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130229622</v>
+        <v>130229093</v>
       </c>
       <c r="B26" t="n">
-        <v>97794</v>
+        <v>92026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540146</v>
+        <v>540129</v>
       </c>
       <c r="R26" t="n">
-        <v>6703918</v>
+        <v>6703915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,7 +3456,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,12 +3466,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130228529</v>
+        <v>130228096</v>
       </c>
       <c r="B7" t="n">
         <v>91728</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540105</v>
+        <v>540116</v>
       </c>
       <c r="R7" t="n">
-        <v>6703987</v>
+        <v>6704044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228096</v>
+        <v>130228529</v>
       </c>
       <c r="B8" t="n">
         <v>91728</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540116</v>
+        <v>540105</v>
       </c>
       <c r="R8" t="n">
-        <v>6704044</v>
+        <v>6703987</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228270</v>
+        <v>130228156</v>
       </c>
       <c r="B13" t="n">
         <v>92026</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540094</v>
+        <v>540107</v>
       </c>
       <c r="R13" t="n">
-        <v>6704020</v>
+        <v>6704044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,12 +1991,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ovanligt stora fruktkroppar.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,7 +2018,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228156</v>
+        <v>130228270</v>
       </c>
       <c r="B14" t="n">
         <v>92026</v>
@@ -2053,7 +2048,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2067,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540107</v>
+        <v>540094</v>
       </c>
       <c r="R14" t="n">
-        <v>6704044</v>
+        <v>6704020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2107,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ovanligt stora fruktkroppar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2479,54 +2479,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130229386</v>
+        <v>130229109</v>
       </c>
       <c r="B18" t="n">
-        <v>92026</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540214</v>
+        <v>540125</v>
       </c>
       <c r="R18" t="n">
-        <v>6703919</v>
+        <v>6703913</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2554,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,12 +2564,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,50 +2698,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130229109</v>
+        <v>130229386</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>92026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540125</v>
+        <v>540214</v>
       </c>
       <c r="R20" t="n">
-        <v>6703913</v>
+        <v>6703919</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2792,7 +2787,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2926,7 +2926,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B22" t="n">
         <v>92026</v>
@@ -2954,17 +2954,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R22" t="n">
-        <v>6704022</v>
+        <v>6703987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,7 +3042,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B23" t="n">
         <v>92026</v>
@@ -3061,26 +3070,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R23" t="n">
-        <v>6703987</v>
+        <v>6704022</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130227845</v>
+        <v>130229622</v>
       </c>
       <c r="B24" t="n">
-        <v>91110</v>
+        <v>97794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,37 +3160,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5685</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540093</v>
+        <v>540146</v>
       </c>
       <c r="R24" t="n">
-        <v>6704106</v>
+        <v>6703918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,12 +3229,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,7 +3243,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3265,45 +3261,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229622</v>
+        <v>130229093</v>
       </c>
       <c r="B25" t="n">
-        <v>97794</v>
+        <v>92026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540146</v>
+        <v>540129</v>
       </c>
       <c r="R25" t="n">
-        <v>6703918</v>
+        <v>6703915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3335,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,12 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,54 +3377,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130229093</v>
+        <v>130227845</v>
       </c>
       <c r="B26" t="n">
-        <v>92026</v>
+        <v>91110</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540129</v>
+        <v>540093</v>
       </c>
       <c r="R26" t="n">
-        <v>6703915</v>
+        <v>6704106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3466,7 +3460,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,6 +3474,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -1010,41 +1010,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130229588</v>
+        <v>130228818</v>
       </c>
       <c r="B5" t="n">
-        <v>97793</v>
+        <v>92026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540144</v>
+        <v>540122</v>
       </c>
       <c r="R5" t="n">
-        <v>6703908</v>
+        <v>6703952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På yta cirka 6x7 meter.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,54 +1126,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130228818</v>
+        <v>130229588</v>
       </c>
       <c r="B6" t="n">
-        <v>92026</v>
+        <v>97793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540122</v>
+        <v>540144</v>
       </c>
       <c r="R6" t="n">
-        <v>6703952</v>
+        <v>6703908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1202,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På yta cirka 6x7 meter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130229042</v>
+        <v>130228156</v>
       </c>
       <c r="B12" t="n">
-        <v>91728</v>
+        <v>92026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540141</v>
+        <v>540107</v>
       </c>
       <c r="R12" t="n">
-        <v>6703928</v>
+        <v>6704044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,7 +1911,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228156</v>
+        <v>130228270</v>
       </c>
       <c r="B13" t="n">
         <v>92026</v>
@@ -1932,7 +1941,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1946,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540107</v>
+        <v>540094</v>
       </c>
       <c r="R13" t="n">
-        <v>6704044</v>
+        <v>6704020</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,7 +2000,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ovanligt stora fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228270</v>
+        <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,43 +2043,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540094</v>
+        <v>540141</v>
       </c>
       <c r="R14" t="n">
-        <v>6704020</v>
+        <v>6703928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,12 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ovanligt stora fruktkroppar.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130229568</v>
+        <v>130229109</v>
       </c>
       <c r="B17" t="n">
-        <v>97797</v>
+        <v>5177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,31 +2369,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2402,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540146</v>
+        <v>540125</v>
       </c>
       <c r="R17" t="n">
-        <v>6703912</v>
+        <v>6703913</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,12 +2443,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,50 +2470,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130229109</v>
+        <v>130229386</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>92026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540125</v>
+        <v>540214</v>
       </c>
       <c r="R18" t="n">
-        <v>6703913</v>
+        <v>6703919</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2564,7 +2559,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130229386</v>
+        <v>130228851</v>
       </c>
       <c r="B20" t="n">
         <v>92026</v>
@@ -2726,26 +2726,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540214</v>
+        <v>540110</v>
       </c>
       <c r="R20" t="n">
-        <v>6703919</v>
+        <v>6703934</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2768,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,12 +2778,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,45 +2805,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130228851</v>
+        <v>130229568</v>
       </c>
       <c r="B21" t="n">
-        <v>92026</v>
+        <v>97797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540110</v>
+        <v>540146</v>
       </c>
       <c r="R21" t="n">
-        <v>6703934</v>
+        <v>6703912</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2894,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229622</v>
+        <v>130227845</v>
       </c>
       <c r="B24" t="n">
-        <v>97794</v>
+        <v>91110</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,34 +3160,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540146</v>
+        <v>540093</v>
       </c>
       <c r="R24" t="n">
-        <v>6703918</v>
+        <v>6704106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,12 +3232,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,6 +3246,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3261,54 +3265,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229093</v>
+        <v>130229622</v>
       </c>
       <c r="B25" t="n">
-        <v>92026</v>
+        <v>97794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540129</v>
+        <v>540146</v>
       </c>
       <c r="R25" t="n">
-        <v>6703915</v>
+        <v>6703918</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3345,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,48 +3377,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130227845</v>
+        <v>130229093</v>
       </c>
       <c r="B26" t="n">
-        <v>91110</v>
+        <v>92026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5685</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540093</v>
+        <v>540129</v>
       </c>
       <c r="R26" t="n">
-        <v>6704106</v>
+        <v>6703915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3456,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,12 +3466,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,7 +3475,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -2465,50 +2465,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130229109</v>
+        <v>130229386</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>92026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540125</v>
+        <v>540214</v>
       </c>
       <c r="R18" t="n">
-        <v>6703913</v>
+        <v>6703919</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,7 +2544,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2550,7 +2554,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,7 +2586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130229386</v>
+        <v>130228851</v>
       </c>
       <c r="B19" t="n">
         <v>92026</v>
@@ -2605,26 +2614,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540214</v>
+        <v>540110</v>
       </c>
       <c r="R19" t="n">
-        <v>6703919</v>
+        <v>6703934</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,12 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,45 +2693,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130228851</v>
+        <v>130229109</v>
       </c>
       <c r="B20" t="n">
-        <v>92026</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540110</v>
+        <v>540125</v>
       </c>
       <c r="R20" t="n">
-        <v>6703934</v>
+        <v>6703913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130229287</v>
       </c>
       <c r="B3" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130227543</v>
       </c>
       <c r="B4" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,54 +1010,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130228818</v>
+        <v>130229588</v>
       </c>
       <c r="B5" t="n">
-        <v>92026</v>
+        <v>97796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>224363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540122</v>
+        <v>540144</v>
       </c>
       <c r="R5" t="n">
-        <v>6703952</v>
+        <v>6703908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På yta cirka 6x7 meter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,41 +1118,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130229588</v>
+        <v>130228818</v>
       </c>
       <c r="B6" t="n">
-        <v>97793</v>
+        <v>92029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540144</v>
+        <v>540122</v>
       </c>
       <c r="R6" t="n">
-        <v>6703908</v>
+        <v>6703952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På yta cirka 6x7 meter.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>130228096</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>130228529</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>540105</v>
       </c>
       <c r="R8" t="n">
-        <v>6703986</v>
+        <v>6703987</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
         <v>130228618</v>
       </c>
       <c r="B9" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>130232204</v>
       </c>
       <c r="B10" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>130227983</v>
       </c>
       <c r="B11" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130229042</v>
+        <v>130228156</v>
       </c>
       <c r="B12" t="n">
-        <v>91728</v>
+        <v>92029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540141</v>
+        <v>540107</v>
       </c>
       <c r="R12" t="n">
-        <v>6703928</v>
+        <v>6704044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,7 +1914,7 @@
         <v>130228270</v>
       </c>
       <c r="B13" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228156</v>
+        <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>92026</v>
+        <v>91731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,43 +2043,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540107</v>
+        <v>540141</v>
       </c>
       <c r="R14" t="n">
-        <v>6704044</v>
+        <v>6703928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,7 +2142,7 @@
         <v>130229463</v>
       </c>
       <c r="B15" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>130227990</v>
       </c>
       <c r="B16" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130228342</v>
+        <v>130229386</v>
       </c>
       <c r="B17" t="n">
-        <v>91728</v>
+        <v>92029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,34 +2369,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540101</v>
+        <v>540214</v>
       </c>
       <c r="R17" t="n">
-        <v>6704020</v>
+        <v>6703919</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2438,7 +2447,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130229386</v>
+        <v>130228342</v>
       </c>
       <c r="B18" t="n">
-        <v>92026</v>
+        <v>91731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,43 +2490,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540214</v>
+        <v>540101</v>
       </c>
       <c r="R18" t="n">
-        <v>6703919</v>
+        <v>6704020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2554,12 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,7 +2589,7 @@
         <v>130228851</v>
       </c>
       <c r="B19" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>130229568</v>
       </c>
       <c r="B21" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B22" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,17 +2954,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R22" t="n">
-        <v>6704022</v>
+        <v>6703987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B23" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,26 +3070,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R23" t="n">
-        <v>6703986</v>
+        <v>6704022</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>130229093</v>
       </c>
       <c r="B24" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>130227845</v>
       </c>
       <c r="B25" t="n">
-        <v>91110</v>
+        <v>91113</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>130229622</v>
       </c>
       <c r="B26" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130229287</v>
       </c>
       <c r="B3" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130227543</v>
       </c>
       <c r="B4" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,41 +1010,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130229588</v>
+        <v>130228818</v>
       </c>
       <c r="B5" t="n">
-        <v>97796</v>
+        <v>92055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540144</v>
+        <v>540122</v>
       </c>
       <c r="R5" t="n">
-        <v>6703908</v>
+        <v>6703952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På yta cirka 6x7 meter.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,54 +1126,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130228818</v>
+        <v>130229588</v>
       </c>
       <c r="B6" t="n">
-        <v>92029</v>
+        <v>97822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540122</v>
+        <v>540144</v>
       </c>
       <c r="R6" t="n">
-        <v>6703952</v>
+        <v>6703908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1202,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På yta cirka 6x7 meter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>130228096</v>
       </c>
       <c r="B7" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>130228529</v>
       </c>
       <c r="B8" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,56 +1448,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228618</v>
+        <v>130232204</v>
       </c>
       <c r="B9" t="n">
-        <v>92029</v>
+        <v>97826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540118</v>
+        <v>540145</v>
       </c>
       <c r="R9" t="n">
-        <v>6703975</v>
+        <v>6703918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,7 +1551,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,59 +1569,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130232204</v>
+        <v>130228618</v>
       </c>
       <c r="B10" t="n">
-        <v>97800</v>
+        <v>92055</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540145</v>
+        <v>540118</v>
       </c>
       <c r="R10" t="n">
-        <v>6703918</v>
+        <v>6703975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,6 +1669,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>130227983</v>
       </c>
       <c r="B11" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130228156</v>
       </c>
       <c r="B12" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>130228270</v>
       </c>
       <c r="B13" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>130229463</v>
       </c>
       <c r="B15" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>130227990</v>
       </c>
       <c r="B16" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>130229386</v>
       </c>
       <c r="B17" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>130228342</v>
       </c>
       <c r="B18" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>130228851</v>
       </c>
       <c r="B19" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>130229568</v>
       </c>
       <c r="B21" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>130228509</v>
       </c>
       <c r="B22" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>130228323</v>
       </c>
       <c r="B23" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>130229093</v>
       </c>
       <c r="B24" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>130227845</v>
       </c>
       <c r="B25" t="n">
-        <v>91113</v>
+        <v>91139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>130229622</v>
       </c>
       <c r="B26" t="n">
-        <v>97797</v>
+        <v>97823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130229287</v>
       </c>
       <c r="B3" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130227543</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130228818</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130229588</v>
       </c>
       <c r="B6" t="n">
-        <v>97822</v>
+        <v>97823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130228096</v>
+        <v>130228529</v>
       </c>
       <c r="B7" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540116</v>
+        <v>540105</v>
       </c>
       <c r="R7" t="n">
-        <v>6704044</v>
+        <v>6703987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228529</v>
+        <v>130228096</v>
       </c>
       <c r="B8" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540105</v>
+        <v>540116</v>
       </c>
       <c r="R8" t="n">
-        <v>6703987</v>
+        <v>6704044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,59 +1448,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130232204</v>
+        <v>130228618</v>
       </c>
       <c r="B9" t="n">
-        <v>97826</v>
+        <v>92056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540145</v>
+        <v>540118</v>
       </c>
       <c r="R9" t="n">
-        <v>6703918</v>
+        <v>6703975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,56 +1567,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130228618</v>
+        <v>130232204</v>
       </c>
       <c r="B10" t="n">
-        <v>92055</v>
+        <v>97827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540118</v>
+        <v>540145</v>
       </c>
       <c r="R10" t="n">
-        <v>6703975</v>
+        <v>6703918</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>130227983</v>
       </c>
       <c r="B11" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228156</v>
+        <v>130228270</v>
       </c>
       <c r="B12" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540107</v>
+        <v>540094</v>
       </c>
       <c r="R12" t="n">
-        <v>6704044</v>
+        <v>6704020</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1884,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ovanligt stora fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228270</v>
+        <v>130228156</v>
       </c>
       <c r="B13" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1955,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540094</v>
+        <v>540107</v>
       </c>
       <c r="R13" t="n">
-        <v>6704020</v>
+        <v>6704044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,12 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ovanligt stora fruktkroppar.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,7 +2035,7 @@
         <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>130229463</v>
       </c>
       <c r="B15" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>130227990</v>
       </c>
       <c r="B16" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>130229386</v>
       </c>
       <c r="B17" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130228342</v>
+        <v>130228851</v>
       </c>
       <c r="B18" t="n">
-        <v>91757</v>
+        <v>92056</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540101</v>
+        <v>540110</v>
       </c>
       <c r="R18" t="n">
-        <v>6704020</v>
+        <v>6703934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,45 +2586,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130228851</v>
+        <v>130229109</v>
       </c>
       <c r="B19" t="n">
-        <v>92055</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540110</v>
+        <v>540125</v>
       </c>
       <c r="R19" t="n">
-        <v>6703934</v>
+        <v>6703913</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,50 +2698,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130229109</v>
+        <v>130228342</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>91758</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540125</v>
+        <v>540101</v>
       </c>
       <c r="R20" t="n">
-        <v>6703913</v>
+        <v>6704020</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,7 +2808,7 @@
         <v>130229568</v>
       </c>
       <c r="B21" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B22" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,26 +2954,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R22" t="n">
-        <v>6703987</v>
+        <v>6704022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +2996,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3006,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B23" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,17 +3061,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R23" t="n">
-        <v>6704022</v>
+        <v>6703987</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,54 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229093</v>
+        <v>130229622</v>
       </c>
       <c r="B24" t="n">
-        <v>92055</v>
+        <v>97824</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540129</v>
+        <v>540146</v>
       </c>
       <c r="R24" t="n">
-        <v>6703915</v>
+        <v>6703918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3229,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,48 +3261,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227845</v>
+        <v>130229093</v>
       </c>
       <c r="B25" t="n">
-        <v>91139</v>
+        <v>92056</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5685</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540093</v>
+        <v>540129</v>
       </c>
       <c r="R25" t="n">
-        <v>6704106</v>
+        <v>6703915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3348,12 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,7 +3359,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3381,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130229622</v>
+        <v>130227845</v>
       </c>
       <c r="B26" t="n">
-        <v>97823</v>
+        <v>91140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,34 +3388,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>5685</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540146</v>
+        <v>540093</v>
       </c>
       <c r="R26" t="n">
-        <v>6703918</v>
+        <v>6704106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,12 +3460,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,6 +3474,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130229287</v>
       </c>
       <c r="B3" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130227543</v>
       </c>
       <c r="B4" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130228818</v>
       </c>
       <c r="B5" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130229588</v>
       </c>
       <c r="B6" t="n">
-        <v>97823</v>
+        <v>97824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>130228529</v>
       </c>
       <c r="B7" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>540105</v>
       </c>
       <c r="R7" t="n">
-        <v>6703987</v>
+        <v>6703986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
         <v>130228096</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>130228618</v>
       </c>
       <c r="B9" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>130232204</v>
       </c>
       <c r="B10" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>130227983</v>
       </c>
       <c r="B11" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228270</v>
+        <v>130228156</v>
       </c>
       <c r="B12" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540094</v>
+        <v>540107</v>
       </c>
       <c r="R12" t="n">
-        <v>6704020</v>
+        <v>6704044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,12 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ovanligt stora fruktkroppar.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228156</v>
+        <v>130228270</v>
       </c>
       <c r="B13" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,7 +1941,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1960,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540107</v>
+        <v>540094</v>
       </c>
       <c r="R13" t="n">
-        <v>6704044</v>
+        <v>6704020</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2000,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ovanligt stora fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,7 +2035,7 @@
         <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>130229463</v>
       </c>
       <c r="B15" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>130227990</v>
       </c>
       <c r="B16" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130229386</v>
+        <v>130228342</v>
       </c>
       <c r="B17" t="n">
-        <v>92056</v>
+        <v>91759</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,43 +2369,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540214</v>
+        <v>540101</v>
       </c>
       <c r="R17" t="n">
-        <v>6703919</v>
+        <v>6704020</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2428,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,12 +2438,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130228851</v>
+        <v>130229386</v>
       </c>
       <c r="B18" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,17 +2493,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540110</v>
+        <v>540214</v>
       </c>
       <c r="R18" t="n">
-        <v>6703934</v>
+        <v>6703919</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2544,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2554,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,50 +2586,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130229109</v>
+        <v>130228851</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>92057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540125</v>
+        <v>540110</v>
       </c>
       <c r="R19" t="n">
-        <v>6703913</v>
+        <v>6703934</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,45 +2693,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130228342</v>
+        <v>130229109</v>
       </c>
       <c r="B20" t="n">
-        <v>91758</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540101</v>
+        <v>540125</v>
       </c>
       <c r="R20" t="n">
-        <v>6704020</v>
+        <v>6703913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,7 +2808,7 @@
         <v>130229568</v>
       </c>
       <c r="B21" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B22" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,17 +2954,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R22" t="n">
-        <v>6704022</v>
+        <v>6703986</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B23" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,26 +3070,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R23" t="n">
-        <v>6703987</v>
+        <v>6704022</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,45 +3149,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229622</v>
+        <v>130229093</v>
       </c>
       <c r="B24" t="n">
-        <v>97824</v>
+        <v>92057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540146</v>
+        <v>540129</v>
       </c>
       <c r="R24" t="n">
-        <v>6703918</v>
+        <v>6703915</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,12 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,54 +3265,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229093</v>
+        <v>130227845</v>
       </c>
       <c r="B25" t="n">
-        <v>92056</v>
+        <v>91141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540129</v>
+        <v>540093</v>
       </c>
       <c r="R25" t="n">
-        <v>6703915</v>
+        <v>6704106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3338,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3348,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3359,6 +3362,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3377,10 +3381,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130227845</v>
+        <v>130229622</v>
       </c>
       <c r="B26" t="n">
-        <v>91140</v>
+        <v>97825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,37 +3392,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5685</v>
+        <v>221946</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540093</v>
+        <v>540146</v>
       </c>
       <c r="R26" t="n">
-        <v>6704106</v>
+        <v>6703918</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,12 +3461,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,7 +3475,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130229287</v>
       </c>
       <c r="B3" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130227543</v>
       </c>
       <c r="B4" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130228818</v>
       </c>
       <c r="B5" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130229588</v>
       </c>
       <c r="B6" t="n">
-        <v>97824</v>
+        <v>97826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130228529</v>
+        <v>130228096</v>
       </c>
       <c r="B7" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540105</v>
+        <v>540116</v>
       </c>
       <c r="R7" t="n">
-        <v>6703986</v>
+        <v>6704044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228096</v>
+        <v>130228529</v>
       </c>
       <c r="B8" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540116</v>
+        <v>540105</v>
       </c>
       <c r="R8" t="n">
-        <v>6704044</v>
+        <v>6703986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,56 +1448,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228618</v>
+        <v>130232204</v>
       </c>
       <c r="B9" t="n">
-        <v>92057</v>
+        <v>97830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540118</v>
+        <v>540145</v>
       </c>
       <c r="R9" t="n">
-        <v>6703975</v>
+        <v>6703918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,7 +1551,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,59 +1569,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130232204</v>
+        <v>130228618</v>
       </c>
       <c r="B10" t="n">
-        <v>97828</v>
+        <v>92059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540145</v>
+        <v>540118</v>
       </c>
       <c r="R10" t="n">
-        <v>6703918</v>
+        <v>6703975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,6 +1669,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>130227983</v>
       </c>
       <c r="B11" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130228156</v>
       </c>
       <c r="B12" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>130228270</v>
       </c>
       <c r="B13" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>130229463</v>
       </c>
       <c r="B15" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>130227990</v>
       </c>
       <c r="B16" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,45 +2358,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130228342</v>
+        <v>130229568</v>
       </c>
       <c r="B17" t="n">
-        <v>91759</v>
+        <v>97830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540101</v>
+        <v>540146</v>
       </c>
       <c r="R17" t="n">
-        <v>6704020</v>
+        <v>6703912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2438,7 +2447,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,7 +2482,7 @@
         <v>130229386</v>
       </c>
       <c r="B18" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2603,7 @@
         <v>130228851</v>
       </c>
       <c r="B19" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,50 +2707,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130229109</v>
+        <v>130228342</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>91761</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540125</v>
+        <v>540101</v>
       </c>
       <c r="R20" t="n">
-        <v>6703913</v>
+        <v>6704020</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2778,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130229568</v>
+        <v>130229109</v>
       </c>
       <c r="B21" t="n">
-        <v>97828</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,31 +2825,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540146</v>
+        <v>540125</v>
       </c>
       <c r="R21" t="n">
-        <v>6703912</v>
+        <v>6703913</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,12 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,7 +2929,7 @@
         <v>130228509</v>
       </c>
       <c r="B22" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>130228323</v>
       </c>
       <c r="B23" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,54 +3149,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229093</v>
+        <v>130227845</v>
       </c>
       <c r="B24" t="n">
-        <v>92057</v>
+        <v>91143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540129</v>
+        <v>540093</v>
       </c>
       <c r="R24" t="n">
-        <v>6703915</v>
+        <v>6704106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3232,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,6 +3246,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3265,48 +3265,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227845</v>
+        <v>130229093</v>
       </c>
       <c r="B25" t="n">
-        <v>91141</v>
+        <v>92059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5685</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540093</v>
+        <v>540129</v>
       </c>
       <c r="R25" t="n">
-        <v>6704106</v>
+        <v>6703915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,7 +3344,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3348,12 +3354,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,7 +3363,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>130229622</v>
       </c>
       <c r="B26" t="n">
-        <v>97825</v>
+        <v>97827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>130229588</v>
       </c>
       <c r="B6" t="n">
-        <v>97826</v>
+        <v>97830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130228096</v>
+        <v>130228529</v>
       </c>
       <c r="B7" t="n">
         <v>91761</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540116</v>
+        <v>540105</v>
       </c>
       <c r="R7" t="n">
-        <v>6704044</v>
+        <v>6703987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228529</v>
+        <v>130228096</v>
       </c>
       <c r="B8" t="n">
         <v>91761</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540105</v>
+        <v>540116</v>
       </c>
       <c r="R8" t="n">
-        <v>6703986</v>
+        <v>6704044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,59 +1448,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130232204</v>
+        <v>130228618</v>
       </c>
       <c r="B9" t="n">
-        <v>97830</v>
+        <v>92059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540145</v>
+        <v>540118</v>
       </c>
       <c r="R9" t="n">
-        <v>6703918</v>
+        <v>6703975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,56 +1567,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130228618</v>
+        <v>130232204</v>
       </c>
       <c r="B10" t="n">
-        <v>92059</v>
+        <v>97834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540118</v>
+        <v>540145</v>
       </c>
       <c r="R10" t="n">
-        <v>6703975</v>
+        <v>6703918</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228156</v>
+        <v>130229042</v>
       </c>
       <c r="B12" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,43 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540107</v>
+        <v>540141</v>
       </c>
       <c r="R12" t="n">
-        <v>6704044</v>
+        <v>6703928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130229042</v>
+        <v>130228156</v>
       </c>
       <c r="B14" t="n">
-        <v>91761</v>
+        <v>92059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,34 +2034,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540141</v>
+        <v>540107</v>
       </c>
       <c r="R14" t="n">
-        <v>6703928</v>
+        <v>6704044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,7 +2142,7 @@
         <v>130229463</v>
       </c>
       <c r="B15" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,54 +2358,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130229568</v>
+        <v>130229386</v>
       </c>
       <c r="B17" t="n">
-        <v>97830</v>
+        <v>92059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540146</v>
+        <v>540214</v>
       </c>
       <c r="R17" t="n">
-        <v>6703912</v>
+        <v>6703919</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,7 +2479,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130229386</v>
+        <v>130228851</v>
       </c>
       <c r="B18" t="n">
         <v>92059</v>
@@ -2507,26 +2507,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540214</v>
+        <v>540110</v>
       </c>
       <c r="R18" t="n">
-        <v>6703919</v>
+        <v>6703934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,12 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130228851</v>
+        <v>130228342</v>
       </c>
       <c r="B19" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2611,21 +2597,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2635,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540110</v>
+        <v>540101</v>
       </c>
       <c r="R19" t="n">
-        <v>6703934</v>
+        <v>6704020</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2680,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,45 +2693,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130228342</v>
+        <v>130229109</v>
       </c>
       <c r="B20" t="n">
-        <v>91761</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540101</v>
+        <v>540125</v>
       </c>
       <c r="R20" t="n">
-        <v>6704020</v>
+        <v>6703913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2768,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2778,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130229109</v>
+        <v>130229568</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>97834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,27 +2816,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540125</v>
+        <v>540146</v>
       </c>
       <c r="R21" t="n">
-        <v>6703913</v>
+        <v>6703912</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2894,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,7 +2926,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B22" t="n">
         <v>92059</v>
@@ -2954,26 +2954,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R22" t="n">
-        <v>6703986</v>
+        <v>6704022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +2996,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3006,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,7 +3033,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B23" t="n">
         <v>92059</v>
@@ -3070,17 +3061,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R23" t="n">
-        <v>6704022</v>
+        <v>6703987</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,48 +3149,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130227845</v>
+        <v>130229093</v>
       </c>
       <c r="B24" t="n">
-        <v>91143</v>
+        <v>92059</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5685</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540093</v>
+        <v>540129</v>
       </c>
       <c r="R24" t="n">
-        <v>6704106</v>
+        <v>6703915</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,12 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,7 +3247,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3265,54 +3265,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229093</v>
+        <v>130227845</v>
       </c>
       <c r="B25" t="n">
-        <v>92059</v>
+        <v>91143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5685</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540129</v>
+        <v>540093</v>
       </c>
       <c r="R25" t="n">
-        <v>6703915</v>
+        <v>6704106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,7 +3338,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3348,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,6 +3362,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>130229622</v>
       </c>
       <c r="B26" t="n">
-        <v>97827</v>
+        <v>97831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -1448,56 +1448,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228618</v>
+        <v>130232204</v>
       </c>
       <c r="B9" t="n">
-        <v>92059</v>
+        <v>97834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540118</v>
+        <v>540145</v>
       </c>
       <c r="R9" t="n">
-        <v>6703975</v>
+        <v>6703918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,7 +1551,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,59 +1569,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130232204</v>
+        <v>130228618</v>
       </c>
       <c r="B10" t="n">
-        <v>97834</v>
+        <v>92059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540145</v>
+        <v>540118</v>
       </c>
       <c r="R10" t="n">
-        <v>6703918</v>
+        <v>6703975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,6 +1669,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130229042</v>
+        <v>130228156</v>
       </c>
       <c r="B12" t="n">
-        <v>91761</v>
+        <v>92059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540141</v>
+        <v>540107</v>
       </c>
       <c r="R12" t="n">
-        <v>6703928</v>
+        <v>6704044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228156</v>
+        <v>130229042</v>
       </c>
       <c r="B14" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,43 +2043,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540107</v>
+        <v>540141</v>
       </c>
       <c r="R14" t="n">
-        <v>6704044</v>
+        <v>6703928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130228851</v>
+        <v>130228342</v>
       </c>
       <c r="B18" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540110</v>
+        <v>540101</v>
       </c>
       <c r="R18" t="n">
-        <v>6703934</v>
+        <v>6704020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130228342</v>
+        <v>130228851</v>
       </c>
       <c r="B19" t="n">
-        <v>91761</v>
+        <v>92059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540101</v>
+        <v>540110</v>
       </c>
       <c r="R19" t="n">
-        <v>6704020</v>
+        <v>6703934</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2926,7 +2926,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B22" t="n">
         <v>92059</v>
@@ -2954,17 +2954,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R22" t="n">
-        <v>6704022</v>
+        <v>6703987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,7 +3042,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B23" t="n">
         <v>92059</v>
@@ -3061,26 +3070,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R23" t="n">
-        <v>6703987</v>
+        <v>6704022</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -1448,59 +1448,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130232204</v>
+        <v>130228618</v>
       </c>
       <c r="B9" t="n">
-        <v>97834</v>
+        <v>92059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540145</v>
+        <v>540118</v>
       </c>
       <c r="R9" t="n">
-        <v>6703918</v>
+        <v>6703975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,56 +1567,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130228618</v>
+        <v>130232204</v>
       </c>
       <c r="B10" t="n">
-        <v>92059</v>
+        <v>97834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540118</v>
+        <v>540145</v>
       </c>
       <c r="R10" t="n">
-        <v>6703975</v>
+        <v>6703918</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228156</v>
+        <v>130229042</v>
       </c>
       <c r="B12" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,43 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540107</v>
+        <v>540141</v>
       </c>
       <c r="R12" t="n">
-        <v>6704044</v>
+        <v>6703928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130229042</v>
+        <v>130228156</v>
       </c>
       <c r="B14" t="n">
-        <v>91761</v>
+        <v>92059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,34 +2034,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540141</v>
+        <v>540107</v>
       </c>
       <c r="R14" t="n">
-        <v>6703928</v>
+        <v>6704044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130228342</v>
+        <v>130228851</v>
       </c>
       <c r="B18" t="n">
-        <v>91761</v>
+        <v>92059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540101</v>
+        <v>540110</v>
       </c>
       <c r="R18" t="n">
-        <v>6704020</v>
+        <v>6703934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130228851</v>
+        <v>130228342</v>
       </c>
       <c r="B19" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540110</v>
+        <v>540101</v>
       </c>
       <c r="R19" t="n">
-        <v>6703934</v>
+        <v>6704020</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2926,7 +2926,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228509</v>
+        <v>130228323</v>
       </c>
       <c r="B22" t="n">
         <v>92059</v>
@@ -2954,26 +2954,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540105</v>
+        <v>540100</v>
       </c>
       <c r="R22" t="n">
-        <v>6703987</v>
+        <v>6704022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +2996,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3006,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,7 +3033,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228323</v>
+        <v>130228509</v>
       </c>
       <c r="B23" t="n">
         <v>92059</v>
@@ -3070,17 +3061,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540100</v>
+        <v>540105</v>
       </c>
       <c r="R23" t="n">
-        <v>6704022</v>
+        <v>6703987</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,54 +3149,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229093</v>
+        <v>130229622</v>
       </c>
       <c r="B24" t="n">
-        <v>92059</v>
+        <v>97831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540129</v>
+        <v>540146</v>
       </c>
       <c r="R24" t="n">
-        <v>6703915</v>
+        <v>6703918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3229,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bredvid plattlummer på liten yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,48 +3261,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227845</v>
+        <v>130229093</v>
       </c>
       <c r="B25" t="n">
-        <v>91143</v>
+        <v>92059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5685</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540093</v>
+        <v>540129</v>
       </c>
       <c r="R25" t="n">
-        <v>6704106</v>
+        <v>6703915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3348,12 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,7 +3359,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3381,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130229622</v>
+        <v>130227845</v>
       </c>
       <c r="B26" t="n">
-        <v>97831</v>
+        <v>91143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,34 +3388,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>5685</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540146</v>
+        <v>540093</v>
       </c>
       <c r="R26" t="n">
-        <v>6703918</v>
+        <v>6704106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,12 +3460,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,6 +3474,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130228074</v>
+        <v>130227211</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540117</v>
+        <v>540127</v>
       </c>
       <c r="R2" t="n">
-        <v>6704045</v>
+        <v>6704138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130229287</v>
+        <v>130227983</v>
       </c>
       <c r="B3" t="n">
-        <v>92059</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,26 +810,17 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540160</v>
+        <v>540139</v>
       </c>
       <c r="R3" t="n">
-        <v>6703877</v>
+        <v>6704099</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130227543</v>
+        <v>130228156</v>
       </c>
       <c r="B4" t="n">
-        <v>91761</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +900,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540097</v>
+        <v>540107</v>
       </c>
       <c r="R4" t="n">
-        <v>6704126</v>
+        <v>6704044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130228818</v>
+        <v>130228270</v>
       </c>
       <c r="B5" t="n">
-        <v>92059</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1035,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1054,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540122</v>
+        <v>540094</v>
       </c>
       <c r="R5" t="n">
-        <v>6703952</v>
+        <v>6704020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1094,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ovanligt stora fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,30 +1126,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130229588</v>
+        <v>130228323</v>
       </c>
       <c r="B6" t="n">
-        <v>97830</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540144</v>
+        <v>540100</v>
       </c>
       <c r="R6" t="n">
-        <v>6703908</v>
+        <v>6704022</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På yta cirka 6x7 meter.</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130228529</v>
+        <v>130228509</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,24 +1244,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
@@ -1304,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228096</v>
+        <v>130228618</v>
       </c>
       <c r="B8" t="n">
-        <v>91761</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,34 +1360,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540116</v>
+        <v>540118</v>
       </c>
       <c r="R8" t="n">
-        <v>6704044</v>
+        <v>6703975</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,6 +1449,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1448,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228618</v>
+        <v>130228818</v>
       </c>
       <c r="B9" t="n">
-        <v>92059</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1498,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1486,18 +1506,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540118</v>
+        <v>540122</v>
       </c>
       <c r="R9" t="n">
-        <v>6703975</v>
+        <v>6703952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,7 +1566,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,59 +1584,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130232204</v>
+        <v>130228851</v>
       </c>
       <c r="B10" t="n">
-        <v>97834</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540145</v>
+        <v>540110</v>
       </c>
       <c r="R10" t="n">
-        <v>6703918</v>
+        <v>6703934</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130227983</v>
+        <v>130229093</v>
       </c>
       <c r="B11" t="n">
-        <v>92059</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,17 +1719,26 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540139</v>
+        <v>540129</v>
       </c>
       <c r="R11" t="n">
-        <v>6704099</v>
+        <v>6703915</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130229042</v>
+        <v>130229203</v>
       </c>
       <c r="B12" t="n">
-        <v>91761</v>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1818,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540141</v>
+        <v>540100</v>
       </c>
       <c r="R12" t="n">
-        <v>6703928</v>
+        <v>6703895</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228270</v>
+        <v>130229287</v>
       </c>
       <c r="B13" t="n">
-        <v>92059</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1944,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1942,14 +1954,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540094</v>
+        <v>540160</v>
       </c>
       <c r="R13" t="n">
-        <v>6704020</v>
+        <v>6703877</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,12 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ovanligt stora fruktkroppar.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228156</v>
+        <v>130229386</v>
       </c>
       <c r="B14" t="n">
-        <v>92059</v>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2060,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2063,14 +2070,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540107</v>
+        <v>540214</v>
       </c>
       <c r="R14" t="n">
-        <v>6704044</v>
+        <v>6703919</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På avverkad del av anmälan, på äldre död ved.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,32 +2151,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130229463</v>
+        <v>130227543</v>
       </c>
       <c r="B15" t="n">
-        <v>97828</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540186</v>
+        <v>540097</v>
       </c>
       <c r="R15" t="n">
-        <v>6703942</v>
+        <v>6704126</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,12 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Yta om 3x8 meter.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,7 +2261,7 @@
         <v>130227990</v>
       </c>
       <c r="B16" t="n">
-        <v>91761</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130229386</v>
+        <v>130228096</v>
       </c>
       <c r="B17" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,43 +2376,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla Svadet, Lilla Svadet, Dlr</t>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540214</v>
+        <v>540116</v>
       </c>
       <c r="R17" t="n">
-        <v>6703919</v>
+        <v>6704044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,12 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På avverkad del av anmälan, på äldre död ved.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130228851</v>
+        <v>130228342</v>
       </c>
       <c r="B18" t="n">
-        <v>92059</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2514,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540110</v>
+        <v>540101</v>
       </c>
       <c r="R18" t="n">
-        <v>6703934</v>
+        <v>6704020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130228342</v>
+        <v>130228529</v>
       </c>
       <c r="B19" t="n">
-        <v>91761</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540101</v>
+        <v>540105</v>
       </c>
       <c r="R19" t="n">
-        <v>6704020</v>
+        <v>6703987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,50 +2686,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130229109</v>
+        <v>130229042</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540125</v>
+        <v>540141</v>
       </c>
       <c r="R20" t="n">
-        <v>6703913</v>
+        <v>6703928</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2778,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130229568</v>
+        <v>130227845</v>
       </c>
       <c r="B21" t="n">
-        <v>97834</v>
+        <v>91282</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,43 +2804,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>5685</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540146</v>
+        <v>540093</v>
       </c>
       <c r="R21" t="n">
-        <v>6703912</v>
+        <v>6704106</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2866,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,12 +2876,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
+          <t>Rikligt på båda sidor av lågan, någon meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,6 +2890,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2926,45 +2909,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130228323</v>
+        <v>130228074</v>
       </c>
       <c r="B22" t="n">
-        <v>92059</v>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540100</v>
+        <v>540117</v>
       </c>
       <c r="R22" t="n">
-        <v>6704022</v>
+        <v>6704045</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +2984,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +2994,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,42 +3021,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228509</v>
+        <v>130228919</v>
       </c>
       <c r="B23" t="n">
-        <v>92059</v>
+        <v>5179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3077,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540105</v>
+        <v>540093</v>
       </c>
       <c r="R23" t="n">
-        <v>6703987</v>
+        <v>6703928</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3096,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3106,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130229622</v>
+        <v>130229109</v>
       </c>
       <c r="B24" t="n">
-        <v>97831</v>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,34 +3144,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540146</v>
+        <v>540125</v>
       </c>
       <c r="R24" t="n">
-        <v>6703918</v>
+        <v>6703913</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3208,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,12 +3218,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bredvid plattlummer på liten yta.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,42 +3245,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130229093</v>
+        <v>130229568</v>
       </c>
       <c r="B25" t="n">
-        <v>92059</v>
+        <v>97989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3305,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540129</v>
+        <v>540146</v>
       </c>
       <c r="R25" t="n">
-        <v>6703915</v>
+        <v>6703912</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Cirka 20 plantor på en yta om cirka 2x2 meter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3366,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130227845</v>
+        <v>130232204</v>
       </c>
       <c r="B26" t="n">
-        <v>91143</v>
+        <v>97989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,37 +3377,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5685</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540093</v>
+        <v>540145</v>
       </c>
       <c r="R26" t="n">
-        <v>6704106</v>
+        <v>6703918</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,12 +3460,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor av lågan, någon meter.</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,7 +3469,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3490,6 +3484,338 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130229463</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>540186</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6703942</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Yta om 3x8 meter.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130229622</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>540146</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6703918</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bredvid plattlummer på liten yta.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130229588</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ramsnäsholm, Rankhyttan, Ramsnäsholm, Rankhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>540144</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6703908</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På yta cirka 6x7 meter.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16488-2025 artfynd.xlsx
+++ b/artfynd/A 16488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227211</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227983</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228156</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228323</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228509</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228618</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228818</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228851</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229093</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1911,6 +1966,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229203</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2027,6 +2087,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229287</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2148,6 +2213,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229386</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227543</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2362,6 +2437,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227990</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2469,6 +2549,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228096</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228342</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2683,6 +2773,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228529</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2790,6 +2885,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229042</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2906,6 +3006,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227845</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3018,6 +3123,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228074</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3130,6 +3240,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228919</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3242,6 +3357,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229109</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3363,6 +3483,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229568</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3484,6 +3609,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130232204</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3596,6 +3726,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229463</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3708,6 +3843,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229622</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3816,8 +3956,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>